--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.14</v>
+        <v>0.06665</v>
       </c>
       <c r="E2">
-        <v>-0.179</v>
+        <v>0.02503</v>
       </c>
       <c r="G2">
-        <v>0.02767164179104478</v>
+        <v>0.03673210892970235</v>
       </c>
       <c r="H2">
-        <v>0.02767164179104478</v>
+        <v>0.03673210892970235</v>
       </c>
       <c r="I2">
-        <v>-0.01128358208955224</v>
+        <v>0.09525015832805572</v>
       </c>
       <c r="J2">
-        <v>-0.009081537132640967</v>
+        <v>0.06931288295746872</v>
       </c>
       <c r="K2">
-        <v>0.396</v>
+        <v>5.380000000000001</v>
       </c>
       <c r="L2">
-        <v>0.01182089552238806</v>
+        <v>0.03407219759341356</v>
       </c>
       <c r="M2">
-        <v>0.13</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>0.007262569832402236</v>
+        <v>0.04043126684636119</v>
       </c>
       <c r="O2">
-        <v>0.3282828282828283</v>
+        <v>0.5576208178438661</v>
       </c>
       <c r="P2">
-        <v>0.13</v>
+        <v>3</v>
       </c>
       <c r="Q2">
-        <v>0.007262569832402236</v>
+        <v>0.04043126684636119</v>
       </c>
       <c r="R2">
-        <v>0.3282828282828283</v>
+        <v>0.5576208178438661</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.43</v>
+        <v>27.88</v>
       </c>
       <c r="V2">
-        <v>0.3033519553072626</v>
+        <v>0.3757412398921834</v>
       </c>
       <c r="W2">
-        <v>0.03771428571428571</v>
+        <v>0.08592931335600698</v>
       </c>
       <c r="X2">
-        <v>0.06745961626579103</v>
+        <v>0.1017303303657859</v>
       </c>
       <c r="Y2">
-        <v>-0.02974533055150531</v>
+        <v>-0.0158010170097789</v>
       </c>
       <c r="Z2">
-        <v>5.068078668683812</v>
+        <v>2.879810322815977</v>
       </c>
       <c r="AA2">
-        <v>-0.04602594462079763</v>
+        <v>0.2003413851526727</v>
       </c>
       <c r="AB2">
-        <v>0.06050148033437901</v>
+        <v>0.0986024470987405</v>
       </c>
       <c r="AC2">
-        <v>-0.1065274249551766</v>
+        <v>0.1017389380539322</v>
       </c>
       <c r="AD2">
-        <v>3.62</v>
+        <v>6.779999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.62</v>
+        <v>6.779999999999999</v>
       </c>
       <c r="AG2">
-        <v>-1.81</v>
+        <v>-21.1</v>
       </c>
       <c r="AH2">
-        <v>0.1682156133828996</v>
+        <v>0.08372437638923191</v>
       </c>
       <c r="AI2">
-        <v>0.169000933706816</v>
+        <v>0.07355174658277282</v>
       </c>
       <c r="AJ2">
-        <v>-0.1124922311995028</v>
+        <v>-0.3973634651600755</v>
       </c>
       <c r="AK2">
-        <v>-0.1131957473420888</v>
+        <v>-0.328149300155521</v>
       </c>
       <c r="AL2">
-        <v>0.048</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AM2">
-        <v>0.048</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AN2">
-        <v>-41.13636363636364</v>
+        <v>0.3974208675263774</v>
       </c>
       <c r="AO2">
-        <v>-7.875</v>
+        <v>26.95340501792114</v>
       </c>
       <c r="AP2">
-        <v>20.56818181818182</v>
+        <v>-1.236811254396248</v>
       </c>
       <c r="AQ2">
-        <v>-7.875</v>
+        <v>26.95340501792114</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Mashreq Insurance Company PLC (PLSE:MIC)</t>
+          <t>Al-Takaful Palestinian Insurance Co. (PLSE:TIC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.14</v>
+        <v>0.0974</v>
       </c>
       <c r="E3">
-        <v>-0.179</v>
+        <v>0.0471</v>
       </c>
       <c r="G3">
-        <v>0.02767164179104478</v>
+        <v>0.04083175803402647</v>
       </c>
       <c r="H3">
-        <v>0.02767164179104478</v>
+        <v>0.04083175803402647</v>
       </c>
       <c r="I3">
-        <v>-0.01128358208955224</v>
+        <v>0.1064272211720227</v>
       </c>
       <c r="J3">
-        <v>-0.009081537132640967</v>
+        <v>0.08179500897623379</v>
       </c>
       <c r="K3">
-        <v>0.396</v>
+        <v>2.45</v>
       </c>
       <c r="L3">
-        <v>0.01182089552238806</v>
+        <v>0.04631379962192817</v>
       </c>
       <c r="M3">
-        <v>0.13</v>
+        <v>1.5</v>
       </c>
       <c r="N3">
-        <v>0.007262569832402236</v>
+        <v>0.05576208178438662</v>
       </c>
       <c r="O3">
-        <v>0.3282828282828283</v>
+        <v>0.6122448979591836</v>
       </c>
       <c r="P3">
-        <v>0.13</v>
+        <v>1.5</v>
       </c>
       <c r="Q3">
-        <v>0.007262569832402236</v>
+        <v>0.05576208178438662</v>
       </c>
       <c r="R3">
-        <v>0.3282828282828283</v>
+        <v>0.6122448979591836</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,207 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.43</v>
+        <v>3.58</v>
       </c>
       <c r="V3">
-        <v>0.3033519553072626</v>
+        <v>0.1330855018587361</v>
       </c>
       <c r="W3">
-        <v>0.03771428571428571</v>
+        <v>0.113953488372093</v>
       </c>
       <c r="X3">
-        <v>0.06745961626579103</v>
+        <v>0.1020073544929388</v>
       </c>
       <c r="Y3">
-        <v>-0.02974533055150531</v>
+        <v>0.01194613387915419</v>
       </c>
       <c r="Z3">
-        <v>5.068078668683812</v>
+        <v>2.614928324270885</v>
       </c>
       <c r="AA3">
-        <v>-0.04602594462079763</v>
+        <v>0.213888085755945</v>
       </c>
       <c r="AB3">
-        <v>0.06050148033437901</v>
+        <v>0.09868348289345132</v>
       </c>
       <c r="AC3">
-        <v>-0.1065274249551766</v>
+        <v>0.1152046028624937</v>
       </c>
       <c r="AD3">
-        <v>3.62</v>
+        <v>2.65</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.62</v>
+        <v>2.65</v>
       </c>
       <c r="AG3">
-        <v>-1.81</v>
+        <v>-0.9300000000000002</v>
       </c>
       <c r="AH3">
-        <v>0.1682156133828996</v>
+        <v>0.08967851099830795</v>
       </c>
       <c r="AI3">
-        <v>0.169000933706816</v>
+        <v>0.1005692599620493</v>
       </c>
       <c r="AJ3">
-        <v>-0.1124922311995028</v>
+        <v>-0.03581055063534849</v>
       </c>
       <c r="AK3">
-        <v>-0.1131957473420888</v>
+        <v>-0.04084321475625824</v>
       </c>
       <c r="AL3">
-        <v>0.048</v>
+        <v>0.066</v>
       </c>
       <c r="AM3">
-        <v>0.048</v>
+        <v>0.066</v>
       </c>
       <c r="AN3">
-        <v>-41.13636363636364</v>
+        <v>0.4233226837060703</v>
       </c>
       <c r="AO3">
-        <v>-7.875</v>
+        <v>85.3030303030303</v>
       </c>
       <c r="AP3">
-        <v>20.56818181818182</v>
+        <v>-0.1485623003194889</v>
       </c>
       <c r="AQ3">
-        <v>-7.875</v>
+        <v>85.3030303030303</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Palestinian Authority</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Trust International Insurance Co. P.L.C (PLSE:TRUST)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0359</v>
+      </c>
+      <c r="E4">
+        <v>0.00296</v>
+      </c>
+      <c r="G4">
+        <v>0.03466666666666667</v>
+      </c>
+      <c r="H4">
+        <v>0.03466666666666667</v>
+      </c>
+      <c r="I4">
+        <v>0.08961904761904763</v>
+      </c>
+      <c r="J4">
+        <v>0.0615532960515167</v>
+      </c>
+      <c r="K4">
+        <v>2.93</v>
+      </c>
+      <c r="L4">
+        <v>0.02790476190476191</v>
+      </c>
+      <c r="M4">
+        <v>1.5</v>
+      </c>
+      <c r="N4">
+        <v>0.03171247357293869</v>
+      </c>
+      <c r="O4">
+        <v>0.5119453924914675</v>
+      </c>
+      <c r="P4">
+        <v>1.5</v>
+      </c>
+      <c r="Q4">
+        <v>0.03171247357293869</v>
+      </c>
+      <c r="R4">
+        <v>0.5119453924914675</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>24.3</v>
+      </c>
+      <c r="V4">
+        <v>0.5137420718816068</v>
+      </c>
+      <c r="W4">
+        <v>0.05790513833992095</v>
+      </c>
+      <c r="X4">
+        <v>0.1014533062386329</v>
+      </c>
+      <c r="Y4">
+        <v>-0.04354816789871196</v>
+      </c>
+      <c r="Z4">
+        <v>3.034682080924855</v>
+      </c>
+      <c r="AA4">
+        <v>0.1867946845494004</v>
+      </c>
+      <c r="AB4">
+        <v>0.09852141130402969</v>
+      </c>
+      <c r="AC4">
+        <v>0.08827327324537068</v>
+      </c>
+      <c r="AD4">
+        <v>4.13</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>4.13</v>
+      </c>
+      <c r="AG4">
+        <v>-20.17</v>
+      </c>
+      <c r="AH4">
+        <v>0.08030332490764146</v>
+      </c>
+      <c r="AI4">
+        <v>0.06273735379006531</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.7434574272023592</v>
+      </c>
+      <c r="AK4">
+        <v>-0.4856730074644836</v>
+      </c>
+      <c r="AL4">
+        <v>0.492</v>
+      </c>
+      <c r="AM4">
+        <v>0.492</v>
+      </c>
+      <c r="AN4">
+        <v>0.3824074074074074</v>
+      </c>
+      <c r="AO4">
+        <v>19.1260162601626</v>
+      </c>
+      <c r="AP4">
+        <v>-1.867592592592593</v>
+      </c>
+      <c r="AQ4">
+        <v>19.1260162601626</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06665</v>
+        <v>0.165</v>
       </c>
       <c r="E2">
-        <v>0.02503</v>
+        <v>-0.0125</v>
       </c>
       <c r="G2">
-        <v>0.03673210892970235</v>
+        <v>0.0946650124069479</v>
       </c>
       <c r="H2">
-        <v>0.03673210892970235</v>
+        <v>0.0946650124069479</v>
       </c>
       <c r="I2">
-        <v>0.09525015832805572</v>
+        <v>0.04937965260545906</v>
       </c>
       <c r="J2">
-        <v>0.06931288295746872</v>
+        <v>0.02986085187055784</v>
       </c>
       <c r="K2">
-        <v>5.380000000000001</v>
+        <v>2.05</v>
       </c>
       <c r="L2">
-        <v>0.03407219759341356</v>
+        <v>0.02543424317617866</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="N2">
-        <v>0.04043126684636119</v>
+        <v>0.04559270516717325</v>
       </c>
       <c r="O2">
-        <v>0.5576208178438661</v>
+        <v>0.7317073170731708</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q2">
-        <v>0.04043126684636119</v>
+        <v>0.04559270516717325</v>
       </c>
       <c r="R2">
-        <v>0.5576208178438661</v>
+        <v>0.7317073170731708</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>27.88</v>
+        <v>18.4</v>
       </c>
       <c r="V2">
-        <v>0.3757412398921834</v>
-      </c>
-      <c r="W2">
-        <v>0.08592931335600698</v>
+        <v>0.5592705167173252</v>
       </c>
       <c r="X2">
-        <v>0.1017303303657859</v>
-      </c>
-      <c r="Y2">
-        <v>-0.0158010170097789</v>
-      </c>
-      <c r="Z2">
-        <v>2.879810322815977</v>
-      </c>
-      <c r="AA2">
-        <v>0.2003413851526727</v>
+        <v>0.1207526571948884</v>
       </c>
       <c r="AB2">
-        <v>0.0986024470987405</v>
-      </c>
-      <c r="AC2">
-        <v>0.1017389380539322</v>
+        <v>0.1134783458859701</v>
       </c>
       <c r="AD2">
-        <v>6.779999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.779999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="AG2">
-        <v>-21.1</v>
+        <v>-14.65</v>
       </c>
       <c r="AH2">
-        <v>0.08372437638923191</v>
+        <v>0.1023192360163711</v>
       </c>
       <c r="AI2">
-        <v>0.07355174658277282</v>
+        <v>0.1361161524500907</v>
       </c>
       <c r="AJ2">
-        <v>-0.3973634651600755</v>
+        <v>-0.8027397260273972</v>
       </c>
       <c r="AK2">
-        <v>-0.328149300155521</v>
+        <v>-1.601092896174863</v>
       </c>
       <c r="AL2">
-        <v>0.5580000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.5580000000000001</v>
+        <v>-0.587</v>
       </c>
       <c r="AN2">
-        <v>0.3974208675263774</v>
-      </c>
-      <c r="AO2">
-        <v>26.95340501792114</v>
+        <v>0.75</v>
       </c>
       <c r="AP2">
-        <v>-1.236811254396248</v>
+        <v>-2.93</v>
       </c>
       <c r="AQ2">
-        <v>26.95340501792114</v>
+        <v>-6.780238500851789</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +695,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al-Takaful Palestinian Insurance Co. (PLSE:TIC)</t>
+          <t>Al-Takaful Palestinian Insurance Company (PLSE:TIC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +704,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0974</v>
+        <v>0.165</v>
       </c>
       <c r="E3">
-        <v>0.0471</v>
+        <v>-0.0125</v>
       </c>
       <c r="G3">
-        <v>0.04083175803402647</v>
+        <v>0.0946650124069479</v>
       </c>
       <c r="H3">
-        <v>0.04083175803402647</v>
+        <v>0.0946650124069479</v>
       </c>
       <c r="I3">
-        <v>0.1064272211720227</v>
+        <v>0.04937965260545906</v>
       </c>
       <c r="J3">
-        <v>0.08179500897623379</v>
+        <v>0.02986085187055784</v>
       </c>
       <c r="K3">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="L3">
-        <v>0.04631379962192817</v>
+        <v>0.02543424317617866</v>
       </c>
       <c r="M3">
         <v>1.5</v>
       </c>
       <c r="N3">
-        <v>0.05576208178438662</v>
+        <v>0.04559270516717325</v>
       </c>
       <c r="O3">
-        <v>0.6122448979591836</v>
+        <v>0.7317073170731708</v>
       </c>
       <c r="P3">
         <v>1.5</v>
       </c>
       <c r="Q3">
-        <v>0.05576208178438662</v>
+        <v>0.04559270516717325</v>
       </c>
       <c r="R3">
-        <v>0.6122448979591836</v>
+        <v>0.7317073170731708</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,207 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.58</v>
+        <v>18.4</v>
       </c>
       <c r="V3">
-        <v>0.1330855018587361</v>
-      </c>
-      <c r="W3">
-        <v>0.113953488372093</v>
+        <v>0.5592705167173252</v>
       </c>
       <c r="X3">
-        <v>0.1020073544929388</v>
-      </c>
-      <c r="Y3">
-        <v>0.01194613387915419</v>
-      </c>
-      <c r="Z3">
-        <v>2.614928324270885</v>
-      </c>
-      <c r="AA3">
-        <v>0.213888085755945</v>
+        <v>0.1207526571948884</v>
       </c>
       <c r="AB3">
-        <v>0.09868348289345132</v>
-      </c>
-      <c r="AC3">
-        <v>0.1152046028624937</v>
+        <v>0.1134783458859701</v>
       </c>
       <c r="AD3">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="AG3">
-        <v>-0.9300000000000002</v>
+        <v>-14.65</v>
       </c>
       <c r="AH3">
-        <v>0.08967851099830795</v>
+        <v>0.1023192360163711</v>
       </c>
       <c r="AI3">
-        <v>0.1005692599620493</v>
+        <v>0.1361161524500907</v>
       </c>
       <c r="AJ3">
-        <v>-0.03581055063534849</v>
+        <v>-0.8027397260273972</v>
       </c>
       <c r="AK3">
-        <v>-0.04084321475625824</v>
+        <v>-1.601092896174863</v>
       </c>
       <c r="AL3">
-        <v>0.066</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.066</v>
+        <v>-0.587</v>
       </c>
       <c r="AN3">
-        <v>0.4233226837060703</v>
-      </c>
-      <c r="AO3">
-        <v>85.3030303030303</v>
+        <v>0.75</v>
       </c>
       <c r="AP3">
-        <v>-0.1485623003194889</v>
+        <v>-2.93</v>
       </c>
       <c r="AQ3">
-        <v>85.3030303030303</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Palestinian Authority</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Trust International Insurance Co. P.L.C (PLSE:TRUST)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.0359</v>
-      </c>
-      <c r="E4">
-        <v>0.00296</v>
-      </c>
-      <c r="G4">
-        <v>0.03466666666666667</v>
-      </c>
-      <c r="H4">
-        <v>0.03466666666666667</v>
-      </c>
-      <c r="I4">
-        <v>0.08961904761904763</v>
-      </c>
-      <c r="J4">
-        <v>0.0615532960515167</v>
-      </c>
-      <c r="K4">
-        <v>2.93</v>
-      </c>
-      <c r="L4">
-        <v>0.02790476190476191</v>
-      </c>
-      <c r="M4">
-        <v>1.5</v>
-      </c>
-      <c r="N4">
-        <v>0.03171247357293869</v>
-      </c>
-      <c r="O4">
-        <v>0.5119453924914675</v>
-      </c>
-      <c r="P4">
-        <v>1.5</v>
-      </c>
-      <c r="Q4">
-        <v>0.03171247357293869</v>
-      </c>
-      <c r="R4">
-        <v>0.5119453924914675</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>24.3</v>
-      </c>
-      <c r="V4">
-        <v>0.5137420718816068</v>
-      </c>
-      <c r="W4">
-        <v>0.05790513833992095</v>
-      </c>
-      <c r="X4">
-        <v>0.1014533062386329</v>
-      </c>
-      <c r="Y4">
-        <v>-0.04354816789871196</v>
-      </c>
-      <c r="Z4">
-        <v>3.034682080924855</v>
-      </c>
-      <c r="AA4">
-        <v>0.1867946845494004</v>
-      </c>
-      <c r="AB4">
-        <v>0.09852141130402969</v>
-      </c>
-      <c r="AC4">
-        <v>0.08827327324537068</v>
-      </c>
-      <c r="AD4">
-        <v>4.13</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>4.13</v>
-      </c>
-      <c r="AG4">
-        <v>-20.17</v>
-      </c>
-      <c r="AH4">
-        <v>0.08030332490764146</v>
-      </c>
-      <c r="AI4">
-        <v>0.06273735379006531</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.7434574272023592</v>
-      </c>
-      <c r="AK4">
-        <v>-0.4856730074644836</v>
-      </c>
-      <c r="AL4">
-        <v>0.492</v>
-      </c>
-      <c r="AM4">
-        <v>0.492</v>
-      </c>
-      <c r="AN4">
-        <v>0.3824074074074074</v>
-      </c>
-      <c r="AO4">
-        <v>19.1260162601626</v>
-      </c>
-      <c r="AP4">
-        <v>-1.867592592592593</v>
-      </c>
-      <c r="AQ4">
-        <v>19.1260162601626</v>
+        <v>-6.780238500851789</v>
       </c>
     </row>
   </sheetData>
